--- a/artfynd/A 5952-2026 artfynd.xlsx
+++ b/artfynd/A 5952-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112831635</v>
       </c>
       <c r="B2" t="n">
-        <v>89955</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +713,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598542</v>
+        <v>598543</v>
       </c>
       <c r="R2" t="n">
         <v>6784744</v>
@@ -778,6 +773,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>116260914</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norrbo 1:3, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>598544</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6784732</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5952-2026 artfynd.xlsx
+++ b/artfynd/A 5952-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,48 +776,64 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116260914</v>
+        <v>134566566</v>
       </c>
       <c r="B3" t="n">
-        <v>104628</v>
+        <v>58415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrbo 1:3, Hls</t>
+          <t>Norrbo-Norrbobäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598544</v>
+        <v>598500</v>
       </c>
       <c r="R3" t="n">
-        <v>6784732</v>
+        <v>6784776</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,6 +886,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>116260914</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrbo 1:3, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598544</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6784732</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
